--- a/hira_material_automation/output/monthly/202601_202605__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__arthroscopy_cannula__041001__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>23752</t>
@@ -519,7 +523,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>22600</t>
@@ -552,7 +560,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>22435</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:06:51</t>
+          <t>2026-05-14T22:15:03</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e9568716bf0905b7c8a472e09bd8741f035cfe083a3753a62a071756be0b4869</t>
+          <t>65ac28f66a316cc5aba4d6ff541a4d6772abd2acc1545c4e82bc7c0022d90c1b</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__arthroscopy_cannula__041001__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:15:03</t>
+          <t>2026-05-24T21:59:34</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65ac28f66a316cc5aba4d6ff541a4d6772abd2acc1545c4e82bc7c0022d90c1b</t>
+          <t>c837aa844cb981c8b5bc24fc3ab0c5ee586665094ebb428cec73e10eb27ee9bf</t>
         </is>
       </c>
     </row>
